--- a/Results/Results.out/Goats/reg_out_goat_hin_coefs.xlsx
+++ b/Results/Results.out/Goats/reg_out_goat_hin_coefs.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -68,6 +68,24 @@
     <t xml:space="preserve">ws.coef.sign.bw_kg</t>
   </si>
   <si>
+    <t xml:space="preserve">ws.coef.Met_bw_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.Met_bw_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.sign.Met_bw_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.bw_frac_Mat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.bw_frac_Mat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.sign.BW_frac_Mat</t>
+  </si>
+  <si>
     <t xml:space="preserve">ws.coef.adg_kg_day</t>
   </si>
   <si>
@@ -188,6 +206,30 @@
     <t xml:space="preserve">ws.coef.se.bw_kg.sqd</t>
   </si>
   <si>
+    <t xml:space="preserve">ws.coef.Met_bw_kg.sqt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.Met_bw_kg.sqt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.Met_bw_kg.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.Met_bw_kg.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.bw_frac_Mat.sqt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.bw_frac_Mat.sqt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.bw_frac_Mat.sqd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ws.coef.se.bw_frac_Mat.sqd</t>
+  </si>
+  <si>
     <t xml:space="preserve">ws.coef.adg_kg_day.sqt</t>
   </si>
   <si>
@@ -237,6 +279,12 @@
   </si>
   <si>
     <t xml:space="preserve">vif.bw_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vif.Met_bw_kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vif.BW_frac_Mat</t>
   </si>
   <si>
     <t xml:space="preserve">vif.ADG</t>
@@ -857,6 +905,54 @@
       <c r="CH1" t="s">
         <v>85</v>
       </c>
+      <c r="CI1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>90</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>93</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>94</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>96</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>97</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>98</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>101</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
